--- a/Figure 2/Figure 2-J.xlsx
+++ b/Figure 2/Figure 2-J.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33150BC-0455-4EB3-AE48-50DF13CFC643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1267F748-7BAC-475C-B8D7-C66DC34790CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21260" yWindow="1580" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,8 +127,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>OD510/min/ml)</t>
     </r>
@@ -142,7 +142,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +169,12 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -190,13 +196,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -483,235 +492,236 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>1.7036740000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>1.7186769999999996</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>1.5103020000000003</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>1.343602</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>1.6786689999999993</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>1.2202439999999997</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>1.2735879999999993</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>2.1487630000000002</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>1.278589</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>1.9020469999999996</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>1.5519769999999993</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>1.4552909999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>1.18357</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>1.6153229999999998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>1.4852970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>1.3902779999999995</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>1.9270520000000007</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>1.2652530000000002</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>1.7036739999999995</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>1.091885</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>1.5036339999999999</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>1.6519970000000002</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>1.5336399999999994</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>1.6803360000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>1.9053809999999993</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>2.0054009999999991</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>1.940388</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>1.3852769999999992</v>
       </c>
     </row>
